--- a/data/trans_orig/P45C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388165</t>
+          <t>389289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>419462</t>
+          <t>420815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242314</t>
+          <t>242817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>269082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>640683</t>
+          <t>642553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>680897</t>
+          <t>682381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76234</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85560</t>
+          <t>87113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125108</t>
+          <t>123998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293326</t>
+          <t>293506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320649</t>
+          <t>322837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295922</t>
+          <t>295374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324245</t>
+          <t>323831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>598900</t>
+          <t>597838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>639963</t>
+          <t>638533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69277</t>
+          <t>69161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>42396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69986</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>90755</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130052</t>
+          <t>129728</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415812</t>
+          <t>418366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>454430</t>
+          <t>453801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>133845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152023</t>
+          <t>152254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>561527</t>
+          <t>558067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>601940</t>
+          <t>598702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71417</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106475</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25502</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85239</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123199</t>
+          <t>126537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1038251</t>
+          <t>1035536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1083994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>600663</t>
+          <t>597932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>635544</t>
+          <t>636122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1650546</t>
+          <t>1650477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1708719</t>
+          <t>1710662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131849</t>
+          <t>131986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176971</t>
+          <t>179517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60834</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94635</t>
+          <t>95579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204550</t>
+          <t>202146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260515</t>
+          <t>257131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290661</t>
+          <t>289662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316094</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>506640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532811</t>
+          <t>532774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>806855</t>
+          <t>806347</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>842394</t>
+          <t>843003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>28802</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>53859</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>51810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96878</t>
+          <t>96773</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>215425</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245145</t>
+          <t>244428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1075514</t>
+          <t>1079090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1121465</t>
+          <t>1121296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1303493</t>
+          <t>1305661</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1355857</t>
+          <t>1356307</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>48627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>76981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110299</t>
+          <t>109349</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152231</t>
+          <t>151303</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167536</t>
+          <t>169004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217987</t>
+          <t>217742</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25399</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2708930</t>
+          <t>2702426</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2790441</t>
+          <t>2790520</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2911617</t>
+          <t>2911519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2986945</t>
+          <t>2988720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5639349</t>
+          <t>5644579</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5751174</t>
+          <t>5758835</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>418942</t>
+          <t>419574</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498082</t>
+          <t>501778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327371</t>
+          <t>329072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>397386</t>
+          <t>400844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>771751</t>
+          <t>768094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>879625</t>
+          <t>872374</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72829</t>
+          <t>71779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,47 +3710,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>56351</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>42381</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>73512</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>56351</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>42501</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>72635</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>90401</t>
+          <t>90524</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>134722</t>
+          <t>133159</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>328984</t>
+          <t>329300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363665</t>
+          <t>363268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256252</t>
+          <t>258299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282380</t>
+          <t>281758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596101</t>
+          <t>596149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637535</t>
+          <t>638259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66151</t>
+          <t>66746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50619</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100060</t>
+          <t>99947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140040</t>
+          <t>140381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22370</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336419</t>
+          <t>336756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367870</t>
+          <t>367055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262933</t>
+          <t>262723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292172</t>
+          <t>293245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608584</t>
+          <t>608816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650251</t>
+          <t>650509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38705</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>69530</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62966</t>
+          <t>64948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82229</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>122691</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>514485</t>
+          <t>511297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>550932</t>
+          <t>548901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208003</t>
+          <t>210178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>231085</t>
+          <t>230721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>732790</t>
+          <t>731415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>774521</t>
+          <t>774528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>71361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105803</t>
+          <t>108987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>40473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>97057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137513</t>
+          <t>139485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>934895</t>
+          <t>936369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>986967</t>
+          <t>987259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>630374</t>
+          <t>628435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>669088</t>
+          <t>669638</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1577951</t>
+          <t>1581055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1641674</t>
+          <t>1644554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148804</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197909</t>
+          <t>198947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>82626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120545</t>
+          <t>121368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244898</t>
+          <t>241356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306294</t>
+          <t>304652</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>19831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>409828</t>
+          <t>408988</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>442120</t>
+          <t>441418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>661818</t>
+          <t>662506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>696949</t>
+          <t>696795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1080569</t>
+          <t>1077868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1128303</t>
+          <t>1125789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59677</t>
+          <t>58646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>90509</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>53618</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86684</t>
+          <t>85680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120809</t>
+          <t>123243</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167574</t>
+          <t>171315</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161588</t>
+          <t>162687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192241</t>
+          <t>191676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>916172</t>
+          <t>916838</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>960964</t>
+          <t>962088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1088388</t>
+          <t>1087212</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1145298</t>
+          <t>1145060</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100972</t>
+          <t>99647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115245</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157563</t>
+          <t>157302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193411</t>
+          <t>192350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>246407</t>
+          <t>246246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2751444</t>
+          <t>2753329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2841510</t>
+          <t>2840089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3000918</t>
+          <t>2998116</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3082067</t>
+          <t>3082643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5778900</t>
+          <t>5776567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5902630</t>
+          <t>5897089</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>508519</t>
+          <t>512738</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>597280</t>
+          <t>599710</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>384322</t>
+          <t>378528</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>459134</t>
+          <t>460451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>912731</t>
+          <t>911466</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1028306</t>
+          <t>1029871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>32033</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>59054</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72248</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79788</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>121313</t>
+          <t>122999</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338014</t>
+          <t>336996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>368022</t>
+          <t>369917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256896</t>
+          <t>258814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287509</t>
+          <t>288262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>607758</t>
+          <t>608264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650114</t>
+          <t>649554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53909</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48254</t>
+          <t>46440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77292</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108099</t>
+          <t>107943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148886</t>
+          <t>150644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>316073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341279</t>
+          <t>341808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289820</t>
+          <t>293084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322014</t>
+          <t>322190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>618200</t>
+          <t>616664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657163</t>
+          <t>655313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54054</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68468</t>
+          <t>68019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74726</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112680</t>
+          <t>113853</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434032</t>
+          <t>435311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465762</t>
+          <t>465967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138069</t>
+          <t>137723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154986</t>
+          <t>154314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>580758</t>
+          <t>577582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>615425</t>
+          <t>614291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>48493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80799</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>66954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98655</t>
+          <t>102499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,62 +8758,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7063</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>971114</t>
+          <t>972373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1017691</t>
+          <t>1017473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>690143</t>
+          <t>687524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>728005</t>
+          <t>727048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1674390</t>
+          <t>1674764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1734637</t>
+          <t>1733007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114245</t>
+          <t>112364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158273</t>
+          <t>157308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86559</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124506</t>
+          <t>125829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212144</t>
+          <t>212658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271524</t>
+          <t>269746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>541211</t>
+          <t>543730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>574400</t>
+          <t>574999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>645984</t>
+          <t>646198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>676610</t>
+          <t>676795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1200619</t>
+          <t>1200216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1245623</t>
+          <t>1245529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70092</t>
+          <t>68522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78692</t>
+          <t>78954</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93779</t>
+          <t>95305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>136368</t>
+          <t>138391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202523</t>
+          <t>202118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231280</t>
+          <t>230327</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>901206</t>
+          <t>901447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>946502</t>
+          <t>947563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1111355</t>
+          <t>1113489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1165229</t>
+          <t>1167264</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>47628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74120</t>
+          <t>74219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116920</t>
+          <t>114800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161590</t>
+          <t>159122</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173375</t>
+          <t>175014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224945</t>
+          <t>226126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,82 +10106,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>5964</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>19759</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>17801</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>10260</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>30467</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>11750</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>6173</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>20951</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>11059</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>29930</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2868476</t>
+          <t>2867913</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2947732</t>
+          <t>2945656</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2987505</t>
+          <t>2989245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3069812</t>
+          <t>3068058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5878834</t>
+          <t>5874607</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5990504</t>
+          <t>5988517</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>379148</t>
+          <t>381542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>457926</t>
+          <t>457549</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>396259</t>
+          <t>402315</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>475391</t>
+          <t>478622</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>804157</t>
+          <t>803382</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>914179</t>
+          <t>911060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44065</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>27715</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54078</t>
+          <t>54561</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,47 +10597,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>70326</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>54763</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>89397</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>70326</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>54899</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>88805</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>411294</t>
+          <t>412134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>445663</t>
+          <t>446701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>382504</t>
+          <t>383050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>407406</t>
+          <t>406868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>802339</t>
+          <t>803562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>844785</t>
+          <t>844523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>52950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86948</t>
+          <t>85934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59851</t>
+          <t>58991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97052</t>
+          <t>95500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139401</t>
+          <t>136361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20976</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360139</t>
+          <t>360038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394494</t>
+          <t>395491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311464</t>
+          <t>313091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336997</t>
+          <t>335817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>681710</t>
+          <t>682331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724744</t>
+          <t>726378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>51657</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84542</t>
+          <t>84483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59707</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95797</t>
+          <t>93934</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135201</t>
+          <t>133369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>545390</t>
+          <t>544408</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642037</t>
+          <t>640707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132588</t>
+          <t>133299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148353</t>
+          <t>148527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>686193</t>
+          <t>686623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>790756</t>
+          <t>796362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104530</t>
+          <t>103911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126581</t>
+          <t>128683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>855778</t>
+          <t>857047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>904394</t>
+          <t>905501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>841111</t>
+          <t>838522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>921005</t>
+          <t>924255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1712249</t>
+          <t>1710856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1833616</t>
+          <t>1834519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111155</t>
+          <t>111563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159723</t>
+          <t>158803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50575</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124084</t>
+          <t>124503</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152869</t>
+          <t>161390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266852</t>
+          <t>269124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359798</t>
+          <t>360371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398830</t>
+          <t>399723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>716387</t>
+          <t>719167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>764653</t>
+          <t>764711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1090189</t>
+          <t>1090493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1155082</t>
+          <t>1157993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64937</t>
+          <t>64214</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>101141</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61676</t>
+          <t>62936</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103449</t>
+          <t>101605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136586</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194839</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39721</t>
+          <t>40401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162920</t>
+          <t>161475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>207693</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>642397</t>
+          <t>642107</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>678691</t>
+          <t>679597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>817663</t>
+          <t>818374</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>878039</t>
+          <t>877710</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>29936</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74083</t>
+          <t>75292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77468</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113443</t>
+          <t>115578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115474</t>
+          <t>118440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174025</t>
+          <t>176061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2790288</t>
+          <t>2786627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2982168</t>
+          <t>2953837</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3091670</t>
+          <t>3084950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3218697</t>
+          <t>3226596</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5907647</t>
+          <t>5902078</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6122205</t>
+          <t>6113849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>351297</t>
+          <t>375786</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>520531</t>
+          <t>525909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>319482</t>
+          <t>309962</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>432516</t>
+          <t>437938</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>742770</t>
+          <t>742172</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>931272</t>
+          <t>933697</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37258</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64439</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>80536</t>
+          <t>80477</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>128259</t>
+          <t>128010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>389289</t>
+          <t>389230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>420815</t>
+          <t>421090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242817</t>
+          <t>242582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269082</t>
+          <t>268073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>642553</t>
+          <t>641373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>682381</t>
+          <t>682125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33430</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87113</t>
+          <t>85875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123998</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293506</t>
+          <t>292940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322837</t>
+          <t>321270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295374</t>
+          <t>298245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323831</t>
+          <t>323753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597838</t>
+          <t>599469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638533</t>
+          <t>639517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41676</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69161</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>43886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>69625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91011</t>
+          <t>90955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>129728</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>418366</t>
+          <t>416655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>453801</t>
+          <t>454858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>134305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152254</t>
+          <t>152274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>558067</t>
+          <t>559999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>598702</t>
+          <t>599893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71800</t>
+          <t>70848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>105746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87825</t>
+          <t>87497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126537</t>
+          <t>124886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1035536</t>
+          <t>1035606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1083994</t>
+          <t>1085122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>597932</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>636122</t>
+          <t>635693</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1650477</t>
+          <t>1650567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1710662</t>
+          <t>1710310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131986</t>
+          <t>131397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179517</t>
+          <t>179143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61494</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95579</t>
+          <t>93968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202146</t>
+          <t>204189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257131</t>
+          <t>258874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289662</t>
+          <t>288748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315456</t>
+          <t>315735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>506640</t>
+          <t>506953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532774</t>
+          <t>533239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>806347</t>
+          <t>805681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>843003</t>
+          <t>841002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28802</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53859</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96773</t>
+          <t>95210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215425</t>
+          <t>216533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>244428</t>
+          <t>244330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1079090</t>
+          <t>1076422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1121296</t>
+          <t>1118511</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1305661</t>
+          <t>1304806</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1356307</t>
+          <t>1356107</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>49682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>75982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109349</t>
+          <t>112104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>153851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169004</t>
+          <t>169193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217742</t>
+          <t>217684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2702426</t>
+          <t>2707405</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2790520</t>
+          <t>2790940</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2911519</t>
+          <t>2911684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2988720</t>
+          <t>2986414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5644579</t>
+          <t>5642064</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5758835</t>
+          <t>5751282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>419574</t>
+          <t>420246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>501778</t>
+          <t>499603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>329072</t>
+          <t>329548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>400844</t>
+          <t>398040</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>768094</t>
+          <t>773689</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>872374</t>
+          <t>879394</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71779</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>133159</t>
+          <t>136615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>329300</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363268</t>
+          <t>363529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258299</t>
+          <t>258267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281758</t>
+          <t>281675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596149</t>
+          <t>596442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>638259</t>
+          <t>637455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66746</t>
+          <t>65414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99947</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140381</t>
+          <t>138841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336756</t>
+          <t>334652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367055</t>
+          <t>366977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262723</t>
+          <t>262180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293245</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>608816</t>
+          <t>610622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650509</t>
+          <t>652142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69530</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64948</t>
+          <t>62380</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122691</t>
+          <t>121430</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>511297</t>
+          <t>514306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548901</t>
+          <t>550771</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210178</t>
+          <t>209392</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230721</t>
+          <t>230884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>731415</t>
+          <t>731863</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>774528</t>
+          <t>774631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71361</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108987</t>
+          <t>104501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40473</t>
+          <t>42066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97057</t>
+          <t>96667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139485</t>
+          <t>138033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17069</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>936369</t>
+          <t>934715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>987259</t>
+          <t>986741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>628435</t>
+          <t>628764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>669638</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1581055</t>
+          <t>1581585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1644554</t>
+          <t>1644643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148109</t>
+          <t>148132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198947</t>
+          <t>198826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>82799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121368</t>
+          <t>121127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241356</t>
+          <t>241873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304652</t>
+          <t>304246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>408988</t>
+          <t>410084</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>441418</t>
+          <t>441578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662506</t>
+          <t>660242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>696795</t>
+          <t>696663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1077868</t>
+          <t>1080608</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1125789</t>
+          <t>1128352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>59196</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90509</t>
+          <t>90282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85680</t>
+          <t>87006</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123243</t>
+          <t>121148</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171315</t>
+          <t>168186</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162687</t>
+          <t>161805</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>190799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>916838</t>
+          <t>916571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>962088</t>
+          <t>961463</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1087212</t>
+          <t>1086793</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1145060</t>
+          <t>1141598</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70320</t>
+          <t>70708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99647</t>
+          <t>100195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114633</t>
+          <t>114846</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157302</t>
+          <t>156294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,47 +6602,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>220431</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>195286</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>247774</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>14,4%</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>220431</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>192350</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>246246</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2753329</t>
+          <t>2751128</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2840089</t>
+          <t>2841576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2998116</t>
+          <t>3000682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3082643</t>
+          <t>3079741</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5776567</t>
+          <t>5776771</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5897089</t>
+          <t>5899387</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>512738</t>
+          <t>510522</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>599710</t>
+          <t>597507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>378528</t>
+          <t>381933</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>460451</t>
+          <t>459634</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>911466</t>
+          <t>912816</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1029871</t>
+          <t>1033040</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59054</t>
+          <t>59347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>43349</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>74654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>81237</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>122999</t>
+          <t>122882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>336996</t>
+          <t>338724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369917</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258814</t>
+          <t>257544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288262</t>
+          <t>287999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608264</t>
+          <t>606043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>649554</t>
+          <t>649423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53315</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84980</t>
+          <t>83993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>78215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107943</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150644</t>
+          <t>152585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316073</t>
+          <t>313668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341808</t>
+          <t>340027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293084</t>
+          <t>293843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322190</t>
+          <t>322096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616664</t>
+          <t>616539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655313</t>
+          <t>656720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54082</t>
+          <t>53803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68019</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76908</t>
+          <t>75861</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113853</t>
+          <t>113048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>435311</t>
+          <t>434758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465967</t>
+          <t>466717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137723</t>
+          <t>137556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154314</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>577582</t>
+          <t>579432</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>614291</t>
+          <t>615086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48493</t>
+          <t>48019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78962</t>
+          <t>79259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66954</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102499</t>
+          <t>100317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972373</t>
+          <t>971323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1017473</t>
+          <t>1016424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>687524</t>
+          <t>687005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>727048</t>
+          <t>728071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1674764</t>
+          <t>1676805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1733007</t>
+          <t>1733947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112364</t>
+          <t>113229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157308</t>
+          <t>158917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125829</t>
+          <t>125257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>212441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269746</t>
+          <t>269646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>543730</t>
+          <t>543235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>574999</t>
+          <t>574463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>646198</t>
+          <t>646598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>676795</t>
+          <t>678974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1200216</t>
+          <t>1200446</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1245529</t>
+          <t>1242906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>39434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48888</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78954</t>
+          <t>77621</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95305</t>
+          <t>95800</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138391</t>
+          <t>137005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202118</t>
+          <t>201673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>230327</t>
+          <t>230601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>901447</t>
+          <t>899457</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>947563</t>
+          <t>945670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1113489</t>
+          <t>1112763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1167264</t>
+          <t>1165704</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47628</t>
+          <t>46539</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74219</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114800</t>
+          <t>120572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159122</t>
+          <t>165677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175014</t>
+          <t>175251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226126</t>
+          <t>224880</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>22018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2867913</t>
+          <t>2865673</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2945656</t>
+          <t>2945505</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2989245</t>
+          <t>2985294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3068058</t>
+          <t>3068016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5874607</t>
+          <t>5879511</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5988517</t>
+          <t>5993752</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>381542</t>
+          <t>379716</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>457549</t>
+          <t>457707</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,47 +10449,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>437923</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>398586</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>479477</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>437923</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>402315</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>478622</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>803382</t>
+          <t>801580</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>911060</t>
+          <t>908042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45872</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54763</t>
+          <t>55921</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>89397</t>
+          <t>89672</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>429895</t>
+          <t>462404</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>412134</t>
+          <t>440064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>446701</t>
+          <t>478299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>395227</t>
+          <t>432044</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>383050</t>
+          <t>419054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>406868</t>
+          <t>444069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>825122</t>
+          <t>894447</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>803562</t>
+          <t>871581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>844523</t>
+          <t>916353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68175</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52950</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85934</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>51366</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115377</t>
+          <t>130295</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95500</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136361</t>
+          <t>151651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,22 +11302,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>378902</t>
+          <t>405113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360038</t>
+          <t>386848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395491</t>
+          <t>421402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>325481</t>
+          <t>360666</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313091</t>
+          <t>347280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335817</t>
+          <t>371700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>704383</t>
+          <t>765779</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>682331</t>
+          <t>740908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726378</t>
+          <t>785234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67055</t>
+          <t>72014</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51657</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84483</t>
+          <t>89050</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47211</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>64231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>114265</t>
+          <t>124367</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93934</t>
+          <t>104496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133369</t>
+          <t>146902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29745</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>593972</t>
+          <t>387293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>544408</t>
+          <t>368677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>640707</t>
+          <t>403215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,17 +11953,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>141569</t>
+          <t>159016</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>149375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148527</t>
+          <t>166628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>735541</t>
+          <t>546310</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>686623</t>
+          <t>525322</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>796362</t>
+          <t>565187</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61514</t>
+          <t>70230</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>54931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103911</t>
+          <t>88069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>35602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>84116</t>
+          <t>95810</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>77872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128683</t>
+          <t>114667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>666852</t>
+          <t>470255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>881503</t>
+          <t>956738</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>857047</t>
+          <t>928184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>905501</t>
+          <t>980992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>874388</t>
+          <t>745004</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>838522</t>
+          <t>724557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>924255</t>
+          <t>762772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1755890</t>
+          <t>1701742</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1710856</t>
+          <t>1668099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1834519</t>
+          <t>1732758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134175</t>
+          <t>154318</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>130333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158803</t>
+          <t>182102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92609</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>85343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124503</t>
+          <t>122339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>226784</t>
+          <t>257301</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161390</t>
+          <t>227238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269124</t>
+          <t>291884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -12600,17 +12600,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1030408</t>
+          <t>1127210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>860453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2007811</t>
+          <t>1987663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>380709</t>
+          <t>458464</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>360371</t>
+          <t>435524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>399723</t>
+          <t>478478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>739441</t>
+          <t>717765</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>719167</t>
+          <t>700352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>764711</t>
+          <t>733687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1120151</t>
+          <t>1176229</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1090493</t>
+          <t>1144223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1157993</t>
+          <t>1202138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82185</t>
+          <t>97140</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101141</t>
+          <t>119955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84117</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>79047</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101605</t>
+          <t>110467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>166302</t>
+          <t>191070</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133950</t>
+          <t>168974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194835</t>
+          <t>221001</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473582</t>
+          <t>566457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840675</t>
+          <t>830090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1314257</t>
+          <t>1396548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>189490</t>
+          <t>184238</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161475</t>
+          <t>159445</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207693</t>
+          <t>203574</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>661276</t>
+          <t>737427</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>642107</t>
+          <t>716718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>679597</t>
+          <t>755973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>850767</t>
+          <t>921665</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>818374</t>
+          <t>890189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>877710</t>
+          <t>950053</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>49932</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75292</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>101651</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
+          <t>83841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115578</t>
+          <t>123365</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>142739</t>
+          <t>151583</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118440</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176061</t>
+          <t>181949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>843672</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001285</t>
+          <t>1080900</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2854472</t>
+          <t>2854249</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2786627</t>
+          <t>2803480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2953837</t>
+          <t>2902729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3137380</t>
+          <t>3151921</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3084950</t>
+          <t>3111597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3226596</t>
+          <t>3193499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5991853</t>
+          <t>6006171</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5902078</t>
+          <t>5943304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6113849</t>
+          <t>6071365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>460842</t>
+          <t>522564</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>375786</t>
+          <t>472480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>525909</t>
+          <t>570154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>388740</t>
+          <t>427862</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>309962</t>
+          <t>389261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>437938</t>
+          <t>467035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>849583</t>
+          <t>950426</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>742172</t>
+          <t>893736</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>933697</t>
+          <t>1011951</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>77962</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>49144</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>40902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>68232</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>102603</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>80477</t>
+          <t>89718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>128010</t>
+          <t>133201</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3368773</t>
+          <t>3434981</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3575265</t>
+          <t>3632629</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6944039</t>
+          <t>7067610</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
